--- a/public/dokumentumok/hulladek-lista-2507.xlsx
+++ b/public/dokumentumok/hulladek-lista-2507.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Marketing\Honlap\Honlap 2025\Hulladékkatalógus_VA_KP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Kommunikáció\Honlap\Honlap\Honlap 2025\Honlapra végleges\Letöltések\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869D4F61-2505-4F05-96BA-7759C601B379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6220EFE2-45CC-49DA-959C-CE4E3A156978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CEC00676-2FE3-43FA-B99F-55DCB88E562B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CEC00676-2FE3-43FA-B99F-55DCB88E562B}"/>
   </bookViews>
   <sheets>
-    <sheet name="ÁTI" sheetId="14" r:id="rId1"/>
-    <sheet name="Reptér" sheetId="10" r:id="rId2"/>
-    <sheet name="Csörgőfa" sheetId="11" r:id="rId3"/>
-    <sheet name="Nyíregyháza" sheetId="12" r:id="rId4"/>
+    <sheet name="Győr, ÁTI" sheetId="14" r:id="rId1"/>
+    <sheet name="Győr, Reptéri út" sheetId="10" r:id="rId2"/>
+    <sheet name="Győr, Csörgőfa sor" sheetId="11" r:id="rId3"/>
+    <sheet name="Nyíregyháza, Derkovits u." sheetId="12" r:id="rId4"/>
     <sheet name="szállítás" sheetId="13" r:id="rId5"/>
-    <sheet name="Karitasz" sheetId="15" r:id="rId6"/>
+    <sheet name="Győr, Karitasz" sheetId="15" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1580,9 +1580,6 @@
     <t>éghető hulladék, amely különbözik a 19 02 08-tól és a 19 02 09-től</t>
   </si>
   <si>
-    <t>Reptéri út 6. - KTJ:101696714</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 02 01 08*</t>
   </si>
   <si>
@@ -4397,9 +4394,6 @@
     <t>szennyezett talaj remediációjából származó szilárd hulladék, amely különbözik a 19 13 01-től</t>
   </si>
   <si>
-    <t>Derkovits u. 132.  - KTJ:102962486</t>
-  </si>
-  <si>
     <t>1221-25/2025</t>
   </si>
   <si>
@@ -4451,18 +4445,12 @@
     <t>veszélyes anyagokat tartalmazó folykony, éghető hulladék</t>
   </si>
   <si>
-    <t>Csörgőfa sor 8. - KTJ:100882646</t>
-  </si>
-  <si>
     <t>GY/40/05399-21,24/2021</t>
   </si>
   <si>
     <t>GY-02/13/01969-13/2020</t>
   </si>
   <si>
-    <t>Kandó K. u 17.-  KTJ:102456074</t>
-  </si>
-  <si>
     <t>GY/53/06936-28/2024</t>
   </si>
   <si>
@@ -4490,10 +4478,22 @@
     <t>Műanyagok</t>
   </si>
   <si>
-    <t>Kandó K. u 10.   - KTJ:102941318</t>
-  </si>
-  <si>
     <t>GY/53/00906-16/2021.</t>
+  </si>
+  <si>
+    <t>9027 Győr, Reptéri út 6. - KTJ:101696714</t>
+  </si>
+  <si>
+    <t>9027 Győr, Csörgőfa sor 8. - KTJ:100882646</t>
+  </si>
+  <si>
+    <t>4400 Nyíregyháza, Derkovits u. 132.  - KTJ:102962486</t>
+  </si>
+  <si>
+    <t>9027 Győr, Kandó K. u 10.  - KTJ:102941318</t>
+  </si>
+  <si>
+    <t>9027 Győr, Kandó K. u 17. - KTJ:102456074</t>
   </si>
 </sst>
 </file>
@@ -4902,6 +4902,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4917,9 +4920,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -4938,9 +4938,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 téma">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4978,7 +4978,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5084,7 +5084,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5226,7 +5226,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5242,16 +5242,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>1473</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
-        <v>1474</v>
-      </c>
-      <c r="B2" s="26"/>
+      <c r="A2" s="28" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B2" s="29"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
@@ -5495,10 +5495,10 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>1378</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -5563,16 +5563,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>513</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B2" s="27"/>
+      <c r="A2" s="30" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B2" s="30"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -7781,24 +7781,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>1470</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="D1" s="25" t="s">
-        <v>1470</v>
-      </c>
-      <c r="E1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="D1" s="28" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E1" s="29"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
-        <v>1471</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="D2" s="25" t="s">
-        <v>1472</v>
-      </c>
-      <c r="E2" s="26"/>
+      <c r="A2" s="28" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="D2" s="28" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -7816,10 +7816,10 @@
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>128</v>
@@ -7830,23 +7830,23 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>7</v>
@@ -7854,15 +7854,15 @@
     </row>
     <row r="8" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -7870,42 +7870,42 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>634</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -7926,10 +7926,10 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -7990,7 +7990,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>7</v>
@@ -8006,7 +8006,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>7</v>
@@ -8014,7 +8014,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>97</v>
@@ -8030,7 +8030,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>7</v>
@@ -8038,7 +8038,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>97</v>
@@ -8070,10 +8070,10 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -8086,7 +8086,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>97</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>97</v>
@@ -8110,7 +8110,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>74</v>
@@ -8134,7 +8134,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>97</v>
@@ -8142,7 +8142,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>74</v>
@@ -8150,7 +8150,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>97</v>
@@ -8198,10 +8198,10 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>763</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -8214,26 +8214,26 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>765</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>773</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>775</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -8246,26 +8246,26 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>783</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -8302,18 +8302,18 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>789</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -8350,31 +8350,31 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>24</v>
@@ -8382,15 +8382,15 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>7</v>
@@ -8398,98 +8398,98 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>859</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>861</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>924</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>937</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>946</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -8529,15 +8529,15 @@
         <v>222</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>1059</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -8550,10 +8550,10 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -8566,7 +8566,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>7</v>
@@ -8574,18 +8574,18 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>1082</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>1084</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -8601,175 +8601,175 @@
         <v>494</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>1087</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>1092</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>1094</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>1096</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>1100</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>1104</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>1106</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>1108</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>1110</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>1112</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>1114</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B113" s="3" t="s">
         <v>1116</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B114" s="3" t="s">
         <v>1118</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>1120</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B116" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>1126</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>1128</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B119" s="3" t="s">
         <v>1130</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B120" s="3" t="s">
         <v>1132</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>1134</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B122" s="3" t="s">
         <v>1136</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -8782,18 +8782,18 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B124" s="3" t="s">
         <v>1140</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>1142</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
@@ -8806,39 +8806,39 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>1144</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B128" s="3" t="s">
         <v>1146</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>1148</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B130" s="3" t="s">
         <v>1150</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B134" s="3" t="s">
         <v>1163</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -8878,10 +8878,10 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>1165</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -8953,31 +8953,31 @@
         <v>496</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B146" s="3" t="s">
         <v>1192</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>1194</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B148" s="3" t="s">
         <v>1196</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
@@ -8990,50 +8990,50 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>1328</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>1330</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>1368</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>1400</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>1402</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>1403</v>
       </c>
     </row>
   </sheetData>
@@ -9057,16 +9057,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
-        <v>1452</v>
-      </c>
-      <c r="B1" s="29"/>
+      <c r="A1" s="31" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B1" s="32"/>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B2" s="29"/>
+      <c r="A2" s="31" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
@@ -9078,15 +9078,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>534</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>10</v>
@@ -9094,7 +9094,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>10</v>
@@ -9102,10 +9102,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>1444</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -9118,31 +9118,31 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>553</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>556</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>558</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>10</v>
@@ -9150,10 +9150,10 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>1446</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -9166,50 +9166,50 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>602</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>605</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>609</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>611</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
+        <v>612</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>613</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>654</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -9230,10 +9230,10 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>662</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -9246,10 +9246,10 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>699</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -9270,10 +9270,10 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -9281,7 +9281,7 @@
         <v>83</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -9294,10 +9294,10 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>718</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -9326,7 +9326,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>72</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>74</v>
@@ -9342,7 +9342,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>102</v>
@@ -9366,23 +9366,23 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>745</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>747</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="15" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>74</v>
@@ -9398,7 +9398,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B44" s="15" t="s">
         <v>7</v>
@@ -9470,10 +9470,10 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="B53" s="15" t="s">
         <v>763</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -9486,18 +9486,18 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="B55" s="15" t="s">
         <v>765</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>767</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -9518,10 +9518,10 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
+        <v>776</v>
+      </c>
+      <c r="B59" s="15" t="s">
         <v>777</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -9534,10 +9534,10 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="B61" s="15" t="s">
         <v>779</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -9574,18 +9574,18 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>785</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="15" t="s">
+        <v>786</v>
+      </c>
+      <c r="B67" s="15" t="s">
         <v>787</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -9614,18 +9614,18 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
+        <v>788</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>789</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="B72" s="15" t="s">
         <v>791</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -9633,7 +9633,7 @@
         <v>153</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -9670,50 +9670,50 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="B78" s="15" t="s">
         <v>796</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="B79" s="15" t="s">
         <v>798</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="15" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="15" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="15" t="s">
+        <v>828</v>
+      </c>
+      <c r="B83" s="15" t="s">
         <v>829</v>
-      </c>
-      <c r="B83" s="15" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -9726,18 +9726,18 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="15" t="s">
+        <v>976</v>
+      </c>
+      <c r="B85" s="15" t="s">
         <v>977</v>
-      </c>
-      <c r="B85" s="15" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="15" t="s">
+        <v>978</v>
+      </c>
+      <c r="B86" s="15" t="s">
         <v>979</v>
-      </c>
-      <c r="B86" s="15" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -9750,98 +9750,98 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="15" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="15" t="s">
+        <v>997</v>
+      </c>
+      <c r="B90" s="15" t="s">
         <v>998</v>
-      </c>
-      <c r="B90" s="15" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="15" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B91" s="15" t="s">
         <v>1020</v>
-      </c>
-      <c r="B91" s="15" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="15" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="15" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B94" s="15" t="s">
         <v>1024</v>
-      </c>
-      <c r="B94" s="15" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B95" s="15" t="s">
         <v>1026</v>
-      </c>
-      <c r="B95" s="15" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B96" s="15" t="s">
         <v>1028</v>
-      </c>
-      <c r="B96" s="15" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B97" s="15" t="s">
         <v>1030</v>
-      </c>
-      <c r="B97" s="15" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B98" s="15" t="s">
         <v>1032</v>
-      </c>
-      <c r="B98" s="15" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="15" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B99" s="15" t="s">
         <v>1034</v>
-      </c>
-      <c r="B99" s="15" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -9849,7 +9849,7 @@
         <v>492</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -9862,58 +9862,58 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B102" s="15" t="s">
         <v>1038</v>
-      </c>
-      <c r="B102" s="15" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B103" s="15" t="s">
         <v>1040</v>
-      </c>
-      <c r="B103" s="15" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="15" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="15" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B106" s="15" t="s">
         <v>1049</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B107" s="15" t="s">
         <v>1051</v>
-      </c>
-      <c r="B107" s="15" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="15" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B108" s="15" t="s">
         <v>1053</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -9950,18 +9950,18 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="15" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B113" s="15" t="s">
         <v>1061</v>
-      </c>
-      <c r="B113" s="15" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="15" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B114" s="15" t="s">
         <v>1063</v>
-      </c>
-      <c r="B114" s="15" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
@@ -10025,7 +10025,7 @@
         <v>494</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -10054,10 +10054,10 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="15" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B126" s="15" t="s">
         <v>1090</v>
-      </c>
-      <c r="B126" s="15" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
@@ -10078,34 +10078,34 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B129" s="15" t="s">
         <v>1094</v>
-      </c>
-      <c r="B129" s="15" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="15" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B130" s="15" t="s">
         <v>1096</v>
-      </c>
-      <c r="B130" s="15" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="15" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B131" s="15" t="s">
         <v>1114</v>
-      </c>
-      <c r="B131" s="15" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="15" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B132" s="15" t="s">
         <v>1120</v>
-      </c>
-      <c r="B132" s="15" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="15" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B134" s="15" t="s">
         <v>1142</v>
-      </c>
-      <c r="B134" s="15" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -10134,10 +10134,10 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="15" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B136" s="15" t="s">
         <v>1144</v>
-      </c>
-      <c r="B136" s="15" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -10150,15 +10150,15 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B138" s="15" t="s">
         <v>1146</v>
-      </c>
-      <c r="B138" s="15" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B139" s="15" t="s">
         <v>7</v>
@@ -10166,18 +10166,18 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="15" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B140" s="15" t="s">
         <v>1153</v>
-      </c>
-      <c r="B140" s="15" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="15" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B141" s="15" t="s">
         <v>1155</v>
-      </c>
-      <c r="B141" s="15" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
@@ -10222,10 +10222,10 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B147" s="15" t="s">
         <v>1159</v>
-      </c>
-      <c r="B147" s="15" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
@@ -10238,10 +10238,10 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B149" s="15" t="s">
         <v>1161</v>
-      </c>
-      <c r="B149" s="15" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
@@ -10254,10 +10254,10 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B151" s="15" t="s">
         <v>1163</v>
-      </c>
-      <c r="B151" s="15" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -10270,18 +10270,18 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B153" s="15" t="s">
         <v>1165</v>
-      </c>
-      <c r="B153" s="15" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B154" s="15" t="s">
         <v>1167</v>
-      </c>
-      <c r="B154" s="15" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
@@ -10350,10 +10350,10 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="24" x14ac:dyDescent="0.3">
@@ -10425,63 +10425,63 @@
         <v>496</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B173" s="15" t="s">
         <v>1192</v>
-      </c>
-      <c r="B173" s="15" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B174" s="15" t="s">
         <v>1194</v>
-      </c>
-      <c r="B174" s="15" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B175" s="15" t="s">
         <v>1196</v>
-      </c>
-      <c r="B175" s="15" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B176" s="15" t="s">
         <v>1204</v>
-      </c>
-      <c r="B176" s="15" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B177" s="15" t="s">
         <v>1206</v>
-      </c>
-      <c r="B177" s="15" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B178" s="15" t="s">
         <v>1208</v>
-      </c>
-      <c r="B178" s="15" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B179" s="15" t="s">
         <v>1210</v>
-      </c>
-      <c r="B179" s="15" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
@@ -10502,10 +10502,10 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B182" s="15" t="s">
         <v>1213</v>
-      </c>
-      <c r="B182" s="15" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
@@ -10542,18 +10542,18 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B187" s="15" t="s">
         <v>1215</v>
-      </c>
-      <c r="B187" s="15" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B188" s="15" t="s">
         <v>1217</v>
-      </c>
-      <c r="B188" s="15" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
@@ -10566,10 +10566,10 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B190" s="15" t="s">
         <v>1219</v>
-      </c>
-      <c r="B190" s="15" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -10582,10 +10582,10 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B192" s="15" t="s">
         <v>1221</v>
-      </c>
-      <c r="B192" s="15" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
@@ -10598,34 +10598,34 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B194" s="15" t="s">
         <v>1225</v>
-      </c>
-      <c r="B194" s="15" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B195" s="15" t="s">
         <v>1231</v>
-      </c>
-      <c r="B195" s="15" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B196" s="15" t="s">
         <v>1233</v>
-      </c>
-      <c r="B196" s="15" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B197" s="15" t="s">
         <v>1235</v>
-      </c>
-      <c r="B197" s="15" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
@@ -10646,82 +10646,82 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B200" s="15" t="s">
         <v>1237</v>
-      </c>
-      <c r="B200" s="15" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B201" s="15" t="s">
         <v>1239</v>
-      </c>
-      <c r="B201" s="15" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B202" s="15" t="s">
         <v>1244</v>
-      </c>
-      <c r="B202" s="15" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="24" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B203" s="15" t="s">
         <v>1246</v>
-      </c>
-      <c r="B203" s="15" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B204" s="15" t="s">
         <v>1248</v>
-      </c>
-      <c r="B204" s="15" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B205" s="15" t="s">
         <v>1250</v>
-      </c>
-      <c r="B205" s="15" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B206" s="15" t="s">
         <v>1252</v>
-      </c>
-      <c r="B206" s="15" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="24" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B207" s="15" t="s">
         <v>1254</v>
-      </c>
-      <c r="B207" s="15" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B208" s="15" t="s">
         <v>1258</v>
-      </c>
-      <c r="B208" s="15" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B209" s="15" t="s">
         <v>1260</v>
-      </c>
-      <c r="B209" s="15" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
@@ -10729,7 +10729,7 @@
         <v>510</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
@@ -10758,26 +10758,26 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B214" s="15" t="s">
         <v>1328</v>
-      </c>
-      <c r="B214" s="15" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B215" s="15" t="s">
         <v>1330</v>
-      </c>
-      <c r="B215" s="15" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B216" s="15" t="s">
         <v>1334</v>
-      </c>
-      <c r="B216" s="15" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
@@ -10790,10 +10790,10 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B218" s="16" t="s">
         <v>1340</v>
-      </c>
-      <c r="B218" s="16" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
@@ -10809,23 +10809,23 @@
         <v>423</v>
       </c>
       <c r="B220" s="16" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B221" s="16" t="s">
         <v>1343</v>
-      </c>
-      <c r="B221" s="16" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B222" s="15" t="s">
         <v>1345</v>
-      </c>
-      <c r="B222" s="15" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
@@ -10849,15 +10849,15 @@
         <v>429</v>
       </c>
       <c r="B225" s="15" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B226" s="15" t="s">
         <v>1349</v>
-      </c>
-      <c r="B226" s="15" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
@@ -10886,82 +10886,82 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B230" s="15" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B231" s="15" t="s">
         <v>1353</v>
-      </c>
-      <c r="B231" s="15" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B232" s="15" t="s">
         <v>1355</v>
-      </c>
-      <c r="B232" s="15" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B233" s="15" t="s">
         <v>1357</v>
-      </c>
-      <c r="B233" s="15" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B234" s="15" t="s">
         <v>1359</v>
-      </c>
-      <c r="B234" s="15" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B235" s="15" t="s">
         <v>1361</v>
-      </c>
-      <c r="B235" s="15" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B236" s="15" t="s">
         <v>1363</v>
-      </c>
-      <c r="B236" s="15" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B237" s="15" t="s">
         <v>1365</v>
-      </c>
-      <c r="B237" s="15" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B238" s="15" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B239" s="15" t="s">
         <v>1373</v>
-      </c>
-      <c r="B239" s="15" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
@@ -10974,15 +10974,15 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B241" s="15" t="s">
         <v>1378</v>
-      </c>
-      <c r="B241" s="15" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B242" s="15" t="s">
         <v>316</v>
@@ -11006,18 +11006,18 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B245" s="15" t="s">
         <v>1381</v>
-      </c>
-      <c r="B245" s="15" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B246" s="15" t="s">
         <v>1383</v>
-      </c>
-      <c r="B246" s="15" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
@@ -11046,66 +11046,66 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B250" s="15" t="s">
         <v>1388</v>
-      </c>
-      <c r="B250" s="15" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B252" s="15" t="s">
         <v>1392</v>
-      </c>
-      <c r="B252" s="15" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B253" s="15" t="s">
         <v>1394</v>
-      </c>
-      <c r="B253" s="15" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B254" s="15" t="s">
         <v>1396</v>
-      </c>
-      <c r="B254" s="15" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B255" s="15" t="s">
         <v>1398</v>
-      </c>
-      <c r="B255" s="15" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B256" s="15" t="s">
         <v>1400</v>
-      </c>
-      <c r="B256" s="15" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B257" s="15" t="s">
         <v>1402</v>
-      </c>
-      <c r="B257" s="15" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
@@ -11126,10 +11126,10 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B260" s="15" t="s">
         <v>1404</v>
-      </c>
-      <c r="B260" s="15" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
@@ -11137,7 +11137,7 @@
         <v>502</v>
       </c>
       <c r="B261" s="15" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
@@ -11174,18 +11174,18 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B266" s="15" t="s">
         <v>1413</v>
-      </c>
-      <c r="B266" s="15" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B267" s="15" t="s">
         <v>1417</v>
-      </c>
-      <c r="B267" s="15" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="24" x14ac:dyDescent="0.3">
@@ -11214,10 +11214,10 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B271" s="15" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
   </sheetData>
@@ -11242,10 +11242,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>1441</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="28" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -11257,66 +11257,66 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>514</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>516</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>518</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>520</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>522</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>524</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>528</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -11337,26 +11337,26 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>530</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>532</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>534</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -11369,31 +11369,31 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>536</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>538</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>540</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>10</v>
@@ -11401,15 +11401,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>543</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>7</v>
@@ -11417,26 +11417,26 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>546</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>548</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -11449,15 +11449,15 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>7</v>
@@ -11473,10 +11473,10 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>553</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -11484,12 +11484,12 @@
         <v>490</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>7</v>
@@ -11497,31 +11497,31 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>556</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>560</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>10</v>
@@ -11529,15 +11529,15 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>7</v>
@@ -11545,10 +11545,10 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>565</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -11564,12 +11564,12 @@
         <v>13</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>7</v>
@@ -11577,82 +11577,82 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>569</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>571</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>573</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>575</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>577</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>579</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>581</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>585</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>587</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -11665,31 +11665,31 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="B54" s="11" t="s">
         <v>589</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="B55" s="11" t="s">
         <v>591</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
+        <v>592</v>
+      </c>
+      <c r="B56" s="11" t="s">
         <v>593</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>7</v>
@@ -11697,26 +11697,26 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="B58" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="B59" s="11" t="s">
         <v>598</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B60" s="11" t="s">
         <v>600</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -11737,15 +11737,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>602</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>7</v>
@@ -11761,42 +11761,42 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>605</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
+        <v>606</v>
+      </c>
+      <c r="B67" s="11" t="s">
         <v>607</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="B68" s="11" t="s">
         <v>609</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
+        <v>610</v>
+      </c>
+      <c r="B69" s="11" t="s">
         <v>611</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>613</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -11809,10 +11809,10 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
+        <v>614</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>615</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -11833,7 +11833,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>7</v>
@@ -11841,10 +11841,10 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="B76" s="11" t="s">
         <v>618</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -11857,18 +11857,18 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="B78" s="11" t="s">
         <v>620</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>622</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -11881,95 +11881,95 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
+        <v>623</v>
+      </c>
+      <c r="B81" s="11" t="s">
         <v>624</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B82" s="11" t="s">
         <v>626</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="B83" s="11" t="s">
         <v>628</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="B84" s="11" t="s">
         <v>630</v>
-      </c>
-      <c r="B84" s="11" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="B85" s="11" t="s">
         <v>632</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
+        <v>633</v>
+      </c>
+      <c r="B86" s="11" t="s">
         <v>634</v>
-      </c>
-      <c r="B86" s="11" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="B87" s="11" t="s">
         <v>636</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="B88" s="11" t="s">
         <v>638</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="B89" s="11" t="s">
         <v>640</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="B90" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="B91" s="11" t="s">
         <v>644</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>7</v>
@@ -11977,31 +11977,31 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
+        <v>647</v>
+      </c>
+      <c r="B94" s="11" t="s">
         <v>648</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>7</v>
@@ -12009,23 +12009,23 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
+        <v>651</v>
+      </c>
+      <c r="B97" s="11" t="s">
         <v>652</v>
-      </c>
-      <c r="B97" s="11" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="B98" s="11" t="s">
         <v>654</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>7</v>
@@ -12049,10 +12049,10 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="B102" s="11" t="s">
         <v>657</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -12121,7 +12121,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>7</v>
@@ -12129,10 +12129,10 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="B112" s="11" t="s">
         <v>660</v>
-      </c>
-      <c r="B112" s="11" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -12161,15 +12161,15 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="B116" s="11" t="s">
         <v>662</v>
-      </c>
-      <c r="B116" s="11" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B117" s="11" t="s">
         <v>7</v>
@@ -12177,18 +12177,18 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="B118" s="11" t="s">
         <v>665</v>
-      </c>
-      <c r="B118" s="11" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="B119" s="11" t="s">
         <v>667</v>
-      </c>
-      <c r="B119" s="11" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
@@ -12201,7 +12201,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>7</v>
@@ -12220,28 +12220,28 @@
         <v>61</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
+        <v>670</v>
+      </c>
+      <c r="B124" s="11" t="s">
         <v>671</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="B125" s="11" t="s">
         <v>673</v>
-      </c>
-      <c r="B125" s="11" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>7</v>
@@ -12249,39 +12249,39 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
+        <v>675</v>
+      </c>
+      <c r="B127" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="B127" s="11" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B128" s="11" t="s">
         <v>678</v>
-      </c>
-      <c r="B128" s="11" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="B129" s="11" t="s">
         <v>680</v>
-      </c>
-      <c r="B129" s="11" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="13" t="s">
+        <v>681</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>682</v>
-      </c>
-      <c r="B130" s="11" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>7</v>
@@ -12289,15 +12289,15 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="B132" s="11" t="s">
         <v>685</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>7</v>
@@ -12305,31 +12305,31 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B134" s="11" t="s">
         <v>688</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="B135" s="11" t="s">
         <v>690</v>
-      </c>
-      <c r="B135" s="11" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="B136" s="11" t="s">
         <v>692</v>
-      </c>
-      <c r="B136" s="11" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>7</v>
@@ -12345,7 +12345,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>7</v>
@@ -12353,15 +12353,15 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="B140" s="11" t="s">
         <v>696</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>7</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="B142" s="11" t="s">
         <v>699</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
@@ -12393,10 +12393,10 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="13" t="s">
+        <v>700</v>
+      </c>
+      <c r="B145" s="11" t="s">
         <v>701</v>
-      </c>
-      <c r="B145" s="11" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
@@ -12409,7 +12409,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>7</v>
@@ -12417,7 +12417,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>97</v>
@@ -12441,10 +12441,10 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="B151" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="B151" s="11" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -12457,10 +12457,10 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="13" t="s">
+        <v>706</v>
+      </c>
+      <c r="B153" s="11" t="s">
         <v>707</v>
-      </c>
-      <c r="B153" s="11" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
@@ -12489,7 +12489,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>7</v>
@@ -12497,7 +12497,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="13" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>97</v>
@@ -12505,7 +12505,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="13" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>72</v>
@@ -12521,10 +12521,10 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="13" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
@@ -12537,15 +12537,15 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>78</v>
@@ -12553,7 +12553,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B165" s="11" t="s">
         <v>24</v>
@@ -12561,10 +12561,10 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="B166" s="11" t="s">
         <v>716</v>
-      </c>
-      <c r="B166" s="11" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -12585,10 +12585,10 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="B169" s="11" t="s">
         <v>718</v>
-      </c>
-      <c r="B169" s="11" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
@@ -12617,7 +12617,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>97</v>
@@ -12625,7 +12625,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>72</v>
@@ -12641,10 +12641,10 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="13" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
@@ -12657,10 +12657,10 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
@@ -12673,7 +12673,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>24</v>
@@ -12681,15 +12681,15 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="B181" s="11" t="s">
         <v>725</v>
-      </c>
-      <c r="B181" s="11" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>7</v>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>97</v>
@@ -12705,7 +12705,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>72</v>
@@ -12713,7 +12713,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>74</v>
@@ -12721,15 +12721,15 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B187" s="11" t="s">
         <v>76</v>
@@ -12737,15 +12737,15 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="B188" s="11" t="s">
         <v>733</v>
-      </c>
-      <c r="B188" s="11" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>105</v>
@@ -12753,7 +12753,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="13" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>24</v>
@@ -12761,15 +12761,15 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="B191" s="11" t="s">
         <v>737</v>
-      </c>
-      <c r="B191" s="11" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B192" s="11" t="s">
         <v>102</v>
@@ -12777,7 +12777,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>7</v>
@@ -12809,10 +12809,10 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="13" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B197" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
@@ -12825,15 +12825,15 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>105</v>
@@ -12841,7 +12841,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="13" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>24</v>
@@ -12849,10 +12849,10 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="B202" s="11" t="s">
         <v>745</v>
-      </c>
-      <c r="B202" s="11" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
@@ -12865,15 +12865,15 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="B204" s="11" t="s">
         <v>747</v>
-      </c>
-      <c r="B204" s="11" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="12" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>7</v>
@@ -12881,7 +12881,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="13" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>97</v>
@@ -12889,7 +12889,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>72</v>
@@ -12897,7 +12897,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>74</v>
@@ -12905,10 +12905,10 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
@@ -12921,10 +12921,10 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="13" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
@@ -12953,7 +12953,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>7</v>
@@ -12961,7 +12961,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>97</v>
@@ -12985,10 +12985,10 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="13" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
@@ -13001,15 +13001,15 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>105</v>
@@ -13025,15 +13025,15 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B224" s="11" t="s">
         <v>760</v>
-      </c>
-      <c r="B224" s="11" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>7</v>
@@ -13097,10 +13097,10 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="12" t="s">
+        <v>762</v>
+      </c>
+      <c r="B233" s="11" t="s">
         <v>763</v>
-      </c>
-      <c r="B233" s="11" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
@@ -13113,23 +13113,23 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="B235" s="11" t="s">
         <v>765</v>
-      </c>
-      <c r="B235" s="11" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="13" t="s">
+        <v>766</v>
+      </c>
+      <c r="B236" s="11" t="s">
         <v>767</v>
-      </c>
-      <c r="B236" s="11" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>7</v>
@@ -13153,15 +13153,15 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="12" t="s">
+        <v>769</v>
+      </c>
+      <c r="B240" s="11" t="s">
         <v>770</v>
-      </c>
-      <c r="B240" s="11" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B241" s="11" t="s">
         <v>7</v>
@@ -13169,18 +13169,18 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="B242" s="11" t="s">
         <v>773</v>
-      </c>
-      <c r="B242" s="11" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="12" t="s">
+        <v>774</v>
+      </c>
+      <c r="B243" s="11" t="s">
         <v>775</v>
-      </c>
-      <c r="B243" s="11" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
@@ -13193,10 +13193,10 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="B245" s="11" t="s">
         <v>777</v>
-      </c>
-      <c r="B245" s="11" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
@@ -13209,18 +13209,18 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="12" t="s">
+        <v>778</v>
+      </c>
+      <c r="B247" s="11" t="s">
         <v>779</v>
-      </c>
-      <c r="B247" s="11" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="13" t="s">
+        <v>780</v>
+      </c>
+      <c r="B248" s="11" t="s">
         <v>781</v>
-      </c>
-      <c r="B248" s="11" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
@@ -13241,10 +13241,10 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="13" t="s">
+        <v>782</v>
+      </c>
+      <c r="B251" s="11" t="s">
         <v>783</v>
-      </c>
-      <c r="B251" s="11" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
@@ -13273,18 +13273,18 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="13" t="s">
+        <v>784</v>
+      </c>
+      <c r="B255" s="11" t="s">
         <v>785</v>
-      </c>
-      <c r="B255" s="11" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="B256" s="11" t="s">
         <v>787</v>
-      </c>
-      <c r="B256" s="11" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
@@ -13313,23 +13313,23 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="B260" s="11" t="s">
         <v>789</v>
-      </c>
-      <c r="B260" s="11" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="13" t="s">
+        <v>790</v>
+      </c>
+      <c r="B261" s="11" t="s">
         <v>791</v>
-      </c>
-      <c r="B261" s="11" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>7</v>
@@ -13377,10 +13377,10 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="13" t="s">
+        <v>793</v>
+      </c>
+      <c r="B268" s="11" t="s">
         <v>794</v>
-      </c>
-      <c r="B268" s="11" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
@@ -13393,55 +13393,55 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="B270" s="11" t="s">
         <v>796</v>
-      </c>
-      <c r="B270" s="11" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="B271" s="11" t="s">
         <v>798</v>
-      </c>
-      <c r="B271" s="11" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="B272" s="11" t="s">
         <v>800</v>
-      </c>
-      <c r="B272" s="11" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A273" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="B273" s="14" t="s">
         <v>802</v>
-      </c>
-      <c r="B273" s="14" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="B274" s="11" t="s">
         <v>804</v>
-      </c>
-      <c r="B274" s="11" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="13" t="s">
+        <v>805</v>
+      </c>
+      <c r="B275" s="11" t="s">
         <v>806</v>
-      </c>
-      <c r="B275" s="11" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>7</v>
@@ -13457,111 +13457,111 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="B278" s="11" t="s">
         <v>809</v>
-      </c>
-      <c r="B278" s="11" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="B279" s="11" t="s">
         <v>811</v>
-      </c>
-      <c r="B279" s="11" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="13" t="s">
+        <v>812</v>
+      </c>
+      <c r="B280" s="11" t="s">
         <v>813</v>
-      </c>
-      <c r="B280" s="11" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="B281" s="11" t="s">
         <v>815</v>
-      </c>
-      <c r="B281" s="11" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="B282" s="11" t="s">
         <v>817</v>
-      </c>
-      <c r="B282" s="11" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="13" t="s">
+        <v>818</v>
+      </c>
+      <c r="B283" s="11" t="s">
         <v>819</v>
-      </c>
-      <c r="B283" s="11" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="13" t="s">
+        <v>820</v>
+      </c>
+      <c r="B284" s="11" t="s">
         <v>821</v>
-      </c>
-      <c r="B284" s="11" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="13" t="s">
+        <v>822</v>
+      </c>
+      <c r="B285" s="11" t="s">
         <v>823</v>
-      </c>
-      <c r="B285" s="11" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="B286" s="11" t="s">
         <v>825</v>
-      </c>
-      <c r="B286" s="11" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="B287" s="11" t="s">
         <v>827</v>
-      </c>
-      <c r="B287" s="11" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="B288" s="11" t="s">
         <v>829</v>
-      </c>
-      <c r="B288" s="11" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="13" t="s">
+        <v>830</v>
+      </c>
+      <c r="B289" s="11" t="s">
         <v>831</v>
-      </c>
-      <c r="B289" s="11" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="B290" s="11" t="s">
         <v>833</v>
-      </c>
-      <c r="B290" s="11" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="13" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B291" s="11" t="s">
         <v>24</v>
@@ -13569,55 +13569,55 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="B292" s="11" t="s">
         <v>836</v>
-      </c>
-      <c r="B292" s="11" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="13" t="s">
+        <v>837</v>
+      </c>
+      <c r="B293" s="11" t="s">
         <v>838</v>
-      </c>
-      <c r="B293" s="11" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="B294" s="11" t="s">
         <v>840</v>
-      </c>
-      <c r="B294" s="11" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="B295" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="B295" s="11" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="B296" s="11" t="s">
         <v>844</v>
-      </c>
-      <c r="B296" s="11" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="B297" s="11" t="s">
         <v>846</v>
-      </c>
-      <c r="B297" s="11" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>7</v>
@@ -13625,87 +13625,87 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="B299" s="11" t="s">
         <v>849</v>
-      </c>
-      <c r="B299" s="11" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="B300" s="11" t="s">
         <v>851</v>
-      </c>
-      <c r="B300" s="11" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="13" t="s">
+        <v>852</v>
+      </c>
+      <c r="B301" s="11" t="s">
         <v>853</v>
-      </c>
-      <c r="B301" s="11" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="B302" s="11" t="s">
         <v>855</v>
-      </c>
-      <c r="B302" s="11" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B303" s="11" t="s">
         <v>857</v>
-      </c>
-      <c r="B303" s="11" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="B304" s="11" t="s">
         <v>859</v>
-      </c>
-      <c r="B304" s="11" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="B305" s="11" t="s">
         <v>861</v>
-      </c>
-      <c r="B305" s="11" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="13" t="s">
+        <v>862</v>
+      </c>
+      <c r="B306" s="11" t="s">
         <v>863</v>
-      </c>
-      <c r="B306" s="11" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="B307" s="11" t="s">
         <v>865</v>
-      </c>
-      <c r="B307" s="11" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="B308" s="11" t="s">
         <v>867</v>
-      </c>
-      <c r="B308" s="11" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="12" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B309" s="11" t="s">
         <v>7</v>
@@ -13713,26 +13713,26 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="B310" s="11" t="s">
         <v>870</v>
-      </c>
-      <c r="B310" s="11" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="13" t="s">
+        <v>871</v>
+      </c>
+      <c r="B311" s="11" t="s">
         <v>872</v>
-      </c>
-      <c r="B311" s="11" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="B312" s="11" t="s">
         <v>874</v>
-      </c>
-      <c r="B312" s="11" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
@@ -13745,18 +13745,18 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="13" t="s">
+        <v>875</v>
+      </c>
+      <c r="B314" s="11" t="s">
         <v>876</v>
-      </c>
-      <c r="B314" s="11" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="B315" s="11" t="s">
         <v>878</v>
-      </c>
-      <c r="B315" s="11" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
@@ -13769,119 +13769,119 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="13" t="s">
+        <v>879</v>
+      </c>
+      <c r="B317" s="11" t="s">
         <v>880</v>
-      </c>
-      <c r="B317" s="11" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="B318" s="11" t="s">
         <v>882</v>
-      </c>
-      <c r="B318" s="11" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="B319" s="11" t="s">
         <v>884</v>
-      </c>
-      <c r="B319" s="11" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="B320" s="11" t="s">
         <v>886</v>
-      </c>
-      <c r="B320" s="11" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="B321" s="11" t="s">
         <v>888</v>
-      </c>
-      <c r="B321" s="11" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="B322" s="11" t="s">
         <v>890</v>
-      </c>
-      <c r="B322" s="11" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="13" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="B324" s="11" t="s">
         <v>893</v>
-      </c>
-      <c r="B324" s="11" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="13" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="B326" s="11" t="s">
         <v>896</v>
-      </c>
-      <c r="B326" s="11" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="13" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="B328" s="11" t="s">
         <v>899</v>
-      </c>
-      <c r="B328" s="11" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="B329" s="11" t="s">
         <v>901</v>
-      </c>
-      <c r="B329" s="11" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="B330" s="11" t="s">
         <v>903</v>
-      </c>
-      <c r="B330" s="11" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="12" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B331" s="11" t="s">
         <v>7</v>
@@ -13905,23 +13905,23 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="B334" s="11" t="s">
         <v>906</v>
-      </c>
-      <c r="B334" s="11" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="13" t="s">
+        <v>907</v>
+      </c>
+      <c r="B335" s="11" t="s">
         <v>908</v>
-      </c>
-      <c r="B335" s="11" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="13" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B336" s="11" t="s">
         <v>198</v>
@@ -13929,34 +13929,34 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="13" t="s">
+        <v>910</v>
+      </c>
+      <c r="B337" s="11" t="s">
         <v>911</v>
-      </c>
-      <c r="B337" s="11" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="13" t="s">
+        <v>912</v>
+      </c>
+      <c r="B338" s="11" t="s">
         <v>913</v>
-      </c>
-      <c r="B338" s="11" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="13" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="B340" s="11" t="s">
         <v>916</v>
-      </c>
-      <c r="B340" s="11" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
@@ -13969,7 +13969,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="12" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B342" s="11" t="s">
         <v>172</v>
@@ -13977,15 +13977,15 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="13" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="12" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B344" s="11" t="s">
         <v>198</v>
@@ -13993,55 +13993,55 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="13" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="13" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="13" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="12" t="s">
+        <v>923</v>
+      </c>
+      <c r="B348" s="11" t="s">
         <v>924</v>
-      </c>
-      <c r="B348" s="11" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="13" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="12" t="s">
+        <v>926</v>
+      </c>
+      <c r="B350" s="11" t="s">
         <v>927</v>
-      </c>
-      <c r="B350" s="11" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B351" s="11" t="s">
         <v>7</v>
@@ -14049,7 +14049,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="12" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B352" s="11" t="s">
         <v>172</v>
@@ -14057,7 +14057,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B353" s="11" t="s">
         <v>174</v>
@@ -14065,15 +14065,15 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="13" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>198</v>
@@ -14081,39 +14081,39 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="13" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="13" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="13" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="B359" s="11" t="s">
         <v>937</v>
-      </c>
-      <c r="B359" s="11" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="12" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B360" s="11" t="s">
         <v>7</v>
@@ -14121,7 +14121,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="12" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B361" s="11" t="s">
         <v>172</v>
@@ -14129,7 +14129,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="12" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B362" s="11" t="s">
         <v>174</v>
@@ -14137,15 +14137,15 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="12" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="12" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B364" s="11" t="s">
         <v>198</v>
@@ -14153,31 +14153,31 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="12" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B365" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="13" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="B367" s="11" t="s">
         <v>946</v>
-      </c>
-      <c r="B367" s="11" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="12" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B368" s="11" t="s">
         <v>7</v>
@@ -14185,10 +14185,10 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="B369" s="11" t="s">
         <v>949</v>
-      </c>
-      <c r="B369" s="11" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
@@ -14209,10 +14209,10 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="13" t="s">
+        <v>950</v>
+      </c>
+      <c r="B372" s="11" t="s">
         <v>951</v>
-      </c>
-      <c r="B372" s="11" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
@@ -14225,79 +14225,79 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="13" t="s">
+        <v>952</v>
+      </c>
+      <c r="B374" s="11" t="s">
         <v>953</v>
-      </c>
-      <c r="B374" s="11" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="B375" s="11" t="s">
         <v>955</v>
-      </c>
-      <c r="B375" s="11" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="12" t="s">
+        <v>956</v>
+      </c>
+      <c r="B376" s="11" t="s">
         <v>957</v>
-      </c>
-      <c r="B376" s="11" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="13" t="s">
+        <v>958</v>
+      </c>
+      <c r="B377" s="11" t="s">
         <v>959</v>
-      </c>
-      <c r="B377" s="11" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="B378" s="11" t="s">
         <v>961</v>
-      </c>
-      <c r="B378" s="11" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="B379" s="11" t="s">
         <v>963</v>
-      </c>
-      <c r="B379" s="11" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="12" t="s">
+        <v>964</v>
+      </c>
+      <c r="B380" s="11" t="s">
         <v>965</v>
-      </c>
-      <c r="B380" s="11" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="13" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B381" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="12" t="s">
+        <v>967</v>
+      </c>
+      <c r="B382" s="11" t="s">
         <v>968</v>
-      </c>
-      <c r="B382" s="11" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="12" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B383" s="11" t="s">
         <v>7</v>
@@ -14313,23 +14313,23 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="13" t="s">
+        <v>970</v>
+      </c>
+      <c r="B385" s="11" t="s">
         <v>971</v>
-      </c>
-      <c r="B385" s="11" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="12" t="s">
+        <v>972</v>
+      </c>
+      <c r="B386" s="11" t="s">
         <v>973</v>
-      </c>
-      <c r="B386" s="11" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="13" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B387" s="11" t="s">
         <v>192</v>
@@ -14345,26 +14345,26 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="13" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B389" s="11" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="B390" s="11" t="s">
         <v>977</v>
-      </c>
-      <c r="B390" s="11" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="13" t="s">
+        <v>978</v>
+      </c>
+      <c r="B391" s="11" t="s">
         <v>979</v>
-      </c>
-      <c r="B391" s="11" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
@@ -14377,39 +14377,39 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="B393" s="11" t="s">
         <v>981</v>
-      </c>
-      <c r="B393" s="11" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="12" t="s">
+        <v>982</v>
+      </c>
+      <c r="B394" s="11" t="s">
         <v>983</v>
-      </c>
-      <c r="B394" s="11" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="B395" s="11" t="s">
         <v>985</v>
-      </c>
-      <c r="B395" s="11" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="12" t="s">
+        <v>986</v>
+      </c>
+      <c r="B396" s="11" t="s">
         <v>987</v>
-      </c>
-      <c r="B396" s="11" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="12" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B397" s="11" t="s">
         <v>7</v>
@@ -14425,10 +14425,10 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="B399" s="11" t="s">
         <v>990</v>
-      </c>
-      <c r="B399" s="11" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
@@ -14457,34 +14457,34 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="13" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B403" s="11" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="B404" s="11" t="s">
         <v>993</v>
-      </c>
-      <c r="B404" s="11" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="13" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B405" s="11" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="B406" s="11" t="s">
         <v>996</v>
-      </c>
-      <c r="B406" s="11" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
@@ -14497,31 +14497,31 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="12" t="s">
+        <v>997</v>
+      </c>
+      <c r="B408" s="11" t="s">
         <v>998</v>
-      </c>
-      <c r="B408" s="11" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="13" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B409" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="12" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B410" s="11" t="s">
         <v>1001</v>
-      </c>
-      <c r="B410" s="11" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="12" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B411" s="11" t="s">
         <v>7</v>
@@ -14529,7 +14529,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="12" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B412" s="11" t="s">
         <v>503</v>
@@ -14553,18 +14553,18 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B415" s="11" t="s">
         <v>1005</v>
-      </c>
-      <c r="B415" s="11" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B416" s="11" t="s">
         <v>1007</v>
-      </c>
-      <c r="B416" s="11" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
@@ -14593,50 +14593,50 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B420" s="11" t="s">
         <v>1009</v>
-      </c>
-      <c r="B420" s="11" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="12" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B421" s="11" t="s">
         <v>1011</v>
-      </c>
-      <c r="B421" s="11" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B422" s="11" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B423" s="11" t="s">
         <v>1014</v>
-      </c>
-      <c r="B423" s="11" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B424" s="11" t="s">
         <v>1016</v>
-      </c>
-      <c r="B424" s="11" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B425" s="11" t="s">
         <v>1018</v>
-      </c>
-      <c r="B425" s="11" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
@@ -14649,74 +14649,74 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="12" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B427" s="11" t="s">
         <v>1020</v>
-      </c>
-      <c r="B427" s="11" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="12" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B428" s="11" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="12" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B429" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B430" s="11" t="s">
         <v>1024</v>
-      </c>
-      <c r="B430" s="11" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="12" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B431" s="11" t="s">
         <v>1026</v>
-      </c>
-      <c r="B431" s="11" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B432" s="11" t="s">
         <v>1028</v>
-      </c>
-      <c r="B432" s="11" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="12" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B433" s="11" t="s">
         <v>1030</v>
-      </c>
-      <c r="B433" s="11" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B434" s="11" t="s">
         <v>1032</v>
-      </c>
-      <c r="B434" s="11" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="12" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B435" s="11" t="s">
         <v>1034</v>
-      </c>
-      <c r="B435" s="11" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
@@ -14724,12 +14724,12 @@
         <v>492</v>
       </c>
       <c r="B436" s="11" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="12" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B437" s="11" t="s">
         <v>7</v>
@@ -14745,79 +14745,79 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="12" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B439" s="11" t="s">
         <v>1038</v>
-      </c>
-      <c r="B439" s="11" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="12" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B440" s="11" t="s">
         <v>1040</v>
-      </c>
-      <c r="B440" s="11" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="12" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B441" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B442" s="11" t="s">
         <v>1043</v>
-      </c>
-      <c r="B442" s="11" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B443" s="11" t="s">
         <v>1045</v>
-      </c>
-      <c r="B443" s="11" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="12" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B444" s="11" t="s">
         <v>1047</v>
-      </c>
-      <c r="B444" s="11" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="13" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B445" s="11" t="s">
         <v>1049</v>
-      </c>
-      <c r="B445" s="11" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="12" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B446" s="11" t="s">
         <v>1051</v>
-      </c>
-      <c r="B446" s="11" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B447" s="11" t="s">
         <v>1053</v>
-      </c>
-      <c r="B447" s="11" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="12" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B448" s="11" t="s">
         <v>7</v>
@@ -14825,10 +14825,10 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="13" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B449" s="11" t="s">
         <v>1056</v>
-      </c>
-      <c r="B449" s="11" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
@@ -14884,15 +14884,15 @@
         <v>222</v>
       </c>
       <c r="B456" s="11" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="12" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B457" s="11" t="s">
         <v>1059</v>
-      </c>
-      <c r="B457" s="11" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
@@ -14905,18 +14905,18 @@
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B459" s="11" t="s">
         <v>1061</v>
-      </c>
-      <c r="B459" s="11" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" s="13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B460" s="11" t="s">
         <v>1063</v>
-      </c>
-      <c r="B460" s="11" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
@@ -14937,7 +14937,7 @@
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" s="12" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B463" s="11" t="s">
         <v>7</v>
@@ -14945,34 +14945,34 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" s="13" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B464" s="11" t="s">
         <v>1066</v>
-      </c>
-      <c r="B464" s="11" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" s="12" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B465" s="11" t="s">
         <v>1068</v>
-      </c>
-      <c r="B465" s="11" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B466" s="11" t="s">
         <v>1070</v>
-      </c>
-      <c r="B466" s="11" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" s="12" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B467" s="11" t="s">
         <v>1072</v>
-      </c>
-      <c r="B467" s="11" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
@@ -14985,7 +14985,7 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" s="12" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B469" s="11" t="s">
         <v>7</v>
@@ -14993,10 +14993,10 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" s="13" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B470" s="11" t="s">
         <v>1075</v>
-      </c>
-      <c r="B470" s="11" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
@@ -15025,23 +15025,23 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" s="13" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B474" s="11" t="s">
         <v>1077</v>
-      </c>
-      <c r="B474" s="11" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" s="13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B475" s="11" t="s">
         <v>1079</v>
-      </c>
-      <c r="B475" s="11" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" s="12" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B476" s="11" t="s">
         <v>7</v>
@@ -15089,18 +15089,18 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" s="13" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B482" s="11" t="s">
         <v>1082</v>
-      </c>
-      <c r="B482" s="11" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" s="13" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B483" s="11" t="s">
         <v>1084</v>
-      </c>
-      <c r="B483" s="11" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
@@ -15116,15 +15116,15 @@
         <v>494</v>
       </c>
       <c r="B485" s="11" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B486" s="11" t="s">
         <v>1087</v>
-      </c>
-      <c r="B486" s="11" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
@@ -15156,7 +15156,7 @@
         <v>253</v>
       </c>
       <c r="B490" s="11" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
@@ -15169,10 +15169,10 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="12" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B492" s="11" t="s">
         <v>1090</v>
-      </c>
-      <c r="B492" s="11" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
@@ -15185,10 +15185,10 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="13" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B494" s="11" t="s">
         <v>1092</v>
-      </c>
-      <c r="B494" s="11" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
@@ -15217,178 +15217,178 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B498" s="11" t="s">
         <v>1094</v>
-      </c>
-      <c r="B498" s="11" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B499" s="11" t="s">
         <v>1096</v>
-      </c>
-      <c r="B499" s="11" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B500" s="11" t="s">
         <v>1098</v>
-      </c>
-      <c r="B500" s="11" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B501" s="11" t="s">
         <v>1100</v>
-      </c>
-      <c r="B501" s="11" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="13" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B502" s="11" t="s">
         <v>1102</v>
-      </c>
-      <c r="B502" s="11" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B503" s="11" t="s">
         <v>1104</v>
-      </c>
-      <c r="B503" s="11" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="13" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B504" s="11" t="s">
         <v>1106</v>
-      </c>
-      <c r="B504" s="11" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="13" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B505" s="11" t="s">
         <v>1108</v>
-      </c>
-      <c r="B505" s="11" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="13" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B506" s="11" t="s">
         <v>1110</v>
-      </c>
-      <c r="B506" s="11" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="13" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B507" s="11" t="s">
         <v>1112</v>
-      </c>
-      <c r="B507" s="11" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="13" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B508" s="11" t="s">
         <v>1114</v>
-      </c>
-      <c r="B508" s="11" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="13" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B509" s="11" t="s">
         <v>1116</v>
-      </c>
-      <c r="B509" s="11" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510" s="13" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B510" s="11" t="s">
         <v>1118</v>
-      </c>
-      <c r="B510" s="11" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="13" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B511" s="11" t="s">
         <v>1120</v>
-      </c>
-      <c r="B511" s="11" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="13" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B512" s="11" t="s">
         <v>1122</v>
-      </c>
-      <c r="B512" s="11" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B513" s="11" t="s">
         <v>1124</v>
-      </c>
-      <c r="B513" s="11" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="13" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B514" s="11" t="s">
         <v>1126</v>
-      </c>
-      <c r="B514" s="11" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="13" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B515" s="11" t="s">
         <v>1128</v>
-      </c>
-      <c r="B515" s="11" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B516" s="11" t="s">
         <v>1130</v>
-      </c>
-      <c r="B516" s="11" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="13" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B517" s="11" t="s">
         <v>1132</v>
-      </c>
-      <c r="B517" s="11" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="13" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B518" s="11" t="s">
         <v>1134</v>
-      </c>
-      <c r="B518" s="11" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="13" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B519" s="11" t="s">
         <v>1136</v>
-      </c>
-      <c r="B519" s="11" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
@@ -15409,26 +15409,26 @@
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="13" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B522" s="11" t="s">
         <v>1138</v>
-      </c>
-      <c r="B522" s="11" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" s="13" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B523" s="11" t="s">
         <v>1140</v>
-      </c>
-      <c r="B523" s="11" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B524" s="11" t="s">
         <v>1142</v>
-      </c>
-      <c r="B524" s="11" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
@@ -15441,10 +15441,10 @@
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="13" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B526" s="11" t="s">
         <v>1144</v>
-      </c>
-      <c r="B526" s="11" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
@@ -15457,31 +15457,31 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="13" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B528" s="11" t="s">
         <v>1146</v>
-      </c>
-      <c r="B528" s="11" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B529" s="11" t="s">
         <v>1148</v>
-      </c>
-      <c r="B529" s="11" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" s="13" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B530" s="11" t="s">
         <v>1150</v>
-      </c>
-      <c r="B530" s="11" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" s="13" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B531" s="11" t="s">
         <v>7</v>
@@ -15489,18 +15489,18 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532" s="13" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B532" s="11" t="s">
         <v>1153</v>
-      </c>
-      <c r="B532" s="11" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" s="13" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B533" s="11" t="s">
         <v>1155</v>
-      </c>
-      <c r="B533" s="11" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
@@ -15513,10 +15513,10 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" s="13" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B535" s="11" t="s">
         <v>1157</v>
-      </c>
-      <c r="B535" s="11" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
@@ -15657,10 +15657,10 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553" s="13" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B553" s="11" t="s">
         <v>1159</v>
-      </c>
-      <c r="B553" s="11" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
@@ -15673,10 +15673,10 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555" s="13" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B555" s="11" t="s">
         <v>1161</v>
-      </c>
-      <c r="B555" s="11" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
@@ -15689,10 +15689,10 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557" s="13" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B557" s="11" t="s">
         <v>1163</v>
-      </c>
-      <c r="B557" s="11" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
@@ -15705,18 +15705,18 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559" s="12" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B559" s="11" t="s">
         <v>1165</v>
-      </c>
-      <c r="B559" s="11" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560" s="12" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B560" s="11" t="s">
         <v>1167</v>
-      </c>
-      <c r="B560" s="11" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
@@ -15777,18 +15777,18 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568" s="13" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B568" s="11" t="s">
         <v>1169</v>
-      </c>
-      <c r="B568" s="11" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569" s="13" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B569" s="11" t="s">
         <v>1171</v>
-      </c>
-      <c r="B569" s="11" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
@@ -15796,7 +15796,7 @@
         <v>326</v>
       </c>
       <c r="B570" s="11" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
@@ -15881,10 +15881,10 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581" s="12" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B581" s="11" t="s">
         <v>1174</v>
-      </c>
-      <c r="B581" s="11" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
@@ -15953,7 +15953,7 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590" s="12" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B590" s="11" t="s">
         <v>7</v>
@@ -15977,34 +15977,34 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" s="12" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B593" s="11" t="s">
         <v>1177</v>
-      </c>
-      <c r="B593" s="11" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" s="12" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B594" s="11" t="s">
         <v>1179</v>
-      </c>
-      <c r="B594" s="11" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" s="13" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B595" s="11" t="s">
         <v>1181</v>
-      </c>
-      <c r="B595" s="11" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" s="13" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B596" s="11" t="s">
         <v>1183</v>
-      </c>
-      <c r="B596" s="11" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
@@ -16017,18 +16017,18 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" s="13" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B598" s="11" t="s">
         <v>1185</v>
-      </c>
-      <c r="B598" s="11" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" s="13" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B599" s="11" t="s">
         <v>1187</v>
-      </c>
-      <c r="B599" s="11" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
@@ -16041,10 +16041,10 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" s="13" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B601" s="11" t="s">
         <v>1189</v>
-      </c>
-      <c r="B601" s="11" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
@@ -16052,47 +16052,47 @@
         <v>496</v>
       </c>
       <c r="B602" s="11" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" s="12" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B603" s="11" t="s">
         <v>1192</v>
-      </c>
-      <c r="B603" s="11" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604" s="13" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B604" s="11" t="s">
         <v>1194</v>
-      </c>
-      <c r="B604" s="11" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" s="12" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B605" s="11" t="s">
         <v>1196</v>
-      </c>
-      <c r="B605" s="11" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" s="13" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B606" s="11" t="s">
         <v>1198</v>
-      </c>
-      <c r="B606" s="11" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B607" s="11" t="s">
         <v>1200</v>
-      </c>
-      <c r="B607" s="11" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
@@ -16116,7 +16116,7 @@
         <v>498</v>
       </c>
       <c r="B610" s="11" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
@@ -16124,39 +16124,39 @@
         <v>500</v>
       </c>
       <c r="B611" s="11" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B612" s="11" t="s">
         <v>1204</v>
-      </c>
-      <c r="B612" s="11" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613" s="12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B613" s="11" t="s">
         <v>1206</v>
-      </c>
-      <c r="B613" s="11" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614" s="12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B614" s="11" t="s">
         <v>1208</v>
-      </c>
-      <c r="B614" s="11" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615" s="13" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B615" s="11" t="s">
         <v>1210</v>
-      </c>
-      <c r="B615" s="11" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
@@ -16164,7 +16164,7 @@
         <v>378</v>
       </c>
       <c r="B616" s="11" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
@@ -16201,10 +16201,10 @@
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621" s="13" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B621" s="11" t="s">
         <v>1213</v>
-      </c>
-      <c r="B621" s="11" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.3">
@@ -16241,18 +16241,18 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" s="12" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B626" s="11" t="s">
         <v>1215</v>
-      </c>
-      <c r="B626" s="11" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" s="12" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B627" s="11" t="s">
         <v>1217</v>
-      </c>
-      <c r="B627" s="11" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
@@ -16265,10 +16265,10 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" s="12" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B629" s="11" t="s">
         <v>1219</v>
-      </c>
-      <c r="B629" s="11" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
@@ -16281,18 +16281,18 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631" s="13" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B631" s="11" t="s">
         <v>1221</v>
-      </c>
-      <c r="B631" s="11" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632" s="13" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B632" s="11" t="s">
         <v>1223</v>
-      </c>
-      <c r="B632" s="11" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
@@ -16313,50 +16313,50 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635" s="12" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B635" s="11" t="s">
         <v>1225</v>
-      </c>
-      <c r="B635" s="11" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636" s="13" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B636" s="11" t="s">
         <v>1227</v>
-      </c>
-      <c r="B636" s="11" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637" s="12" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B637" s="11" t="s">
         <v>1229</v>
-      </c>
-      <c r="B637" s="11" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638" s="13" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B638" s="11" t="s">
         <v>1231</v>
-      </c>
-      <c r="B638" s="11" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" s="12" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B639" s="11" t="s">
         <v>1233</v>
-      </c>
-      <c r="B639" s="11" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" s="13" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B640" s="11" t="s">
         <v>1235</v>
-      </c>
-      <c r="B640" s="11" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
@@ -16385,26 +16385,26 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" s="13" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B644" s="11" t="s">
         <v>1237</v>
-      </c>
-      <c r="B644" s="11" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645" s="12" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B645" s="11" t="s">
         <v>1239</v>
-      </c>
-      <c r="B645" s="11" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" s="13" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B646" s="11" t="s">
         <v>1241</v>
-      </c>
-      <c r="B646" s="11" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
@@ -16420,196 +16420,196 @@
         <v>411</v>
       </c>
       <c r="B648" s="11" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" s="12" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B649" s="11" t="s">
         <v>1244</v>
-      </c>
-      <c r="B649" s="11" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="650" spans="1:2" ht="24" x14ac:dyDescent="0.3">
       <c r="A650" s="12" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B650" s="11" t="s">
         <v>1246</v>
-      </c>
-      <c r="B650" s="11" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B651" s="11" t="s">
         <v>1248</v>
-      </c>
-      <c r="B651" s="11" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" s="12" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B652" s="11" t="s">
         <v>1250</v>
-      </c>
-      <c r="B652" s="11" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" s="12" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B653" s="11" t="s">
         <v>1252</v>
-      </c>
-      <c r="B653" s="11" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B654" s="11" t="s">
         <v>1254</v>
-      </c>
-      <c r="B654" s="11" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655" s="13" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B655" s="11" t="s">
         <v>1256</v>
-      </c>
-      <c r="B655" s="11" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656" s="12" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B656" s="11" t="s">
         <v>1258</v>
-      </c>
-      <c r="B656" s="11" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657" s="12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B657" s="11" t="s">
         <v>1260</v>
-      </c>
-      <c r="B657" s="11" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658" s="12" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B658" s="11" t="s">
         <v>1262</v>
-      </c>
-      <c r="B658" s="11" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659" s="13" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B659" s="11" t="s">
         <v>1264</v>
-      </c>
-      <c r="B659" s="11" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660" s="13" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B660" s="11" t="s">
         <v>1266</v>
-      </c>
-      <c r="B660" s="11" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661" s="13" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B661" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662" s="13" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B662" s="11" t="s">
         <v>1269</v>
-      </c>
-      <c r="B662" s="11" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663" s="13" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B663" s="11" t="s">
         <v>1271</v>
-      </c>
-      <c r="B663" s="11" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664" s="12" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B664" s="11" t="s">
         <v>1273</v>
-      </c>
-      <c r="B664" s="11" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665" s="13" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B665" s="11" t="s">
         <v>1275</v>
-      </c>
-      <c r="B665" s="11" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B666" s="11" t="s">
         <v>1277</v>
-      </c>
-      <c r="B666" s="11" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667" s="13" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B667" s="11" t="s">
         <v>1279</v>
-      </c>
-      <c r="B667" s="11" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668" s="12" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B668" s="11" t="s">
         <v>1281</v>
-      </c>
-      <c r="B668" s="11" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669" s="13" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B669" s="11" t="s">
         <v>1283</v>
-      </c>
-      <c r="B669" s="11" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670" s="12" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B670" s="11" t="s">
         <v>1285</v>
-      </c>
-      <c r="B670" s="11" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B671" s="11" t="s">
         <v>1287</v>
-      </c>
-      <c r="B671" s="11" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672" s="12" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B672" s="11" t="s">
         <v>7</v>
@@ -16620,7 +16620,7 @@
         <v>510</v>
       </c>
       <c r="B673" s="11" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
@@ -16657,18 +16657,18 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678" s="13" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B678" s="11" t="s">
         <v>1291</v>
-      </c>
-      <c r="B678" s="11" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679" s="13" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B679" s="11" t="s">
         <v>1293</v>
-      </c>
-      <c r="B679" s="11" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
@@ -16689,7 +16689,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682" s="12" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B682" s="11" t="s">
         <v>7</v>
@@ -16697,95 +16697,95 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683" s="13" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B683" s="11" t="s">
         <v>1296</v>
-      </c>
-      <c r="B683" s="11" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684" s="12" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B684" s="11" t="s">
         <v>1298</v>
-      </c>
-      <c r="B684" s="11" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685" s="13" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B685" s="11" t="s">
         <v>1300</v>
-      </c>
-      <c r="B685" s="11" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686" s="12" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B686" s="11" t="s">
         <v>1302</v>
-      </c>
-      <c r="B686" s="11" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687" s="12" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B687" s="11" t="s">
         <v>1304</v>
-      </c>
-      <c r="B687" s="11" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688" s="13" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B688" s="11" t="s">
         <v>1306</v>
-      </c>
-      <c r="B688" s="11" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689" s="13" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B689" s="11" t="s">
         <v>1308</v>
-      </c>
-      <c r="B689" s="11" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B690" s="11" t="s">
         <v>1310</v>
-      </c>
-      <c r="B690" s="11" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691" s="12" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B691" s="11" t="s">
         <v>1312</v>
-      </c>
-      <c r="B691" s="11" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B692" s="11" t="s">
         <v>1314</v>
-      </c>
-      <c r="B692" s="11" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B693" s="11" t="s">
         <v>1316</v>
-      </c>
-      <c r="B693" s="11" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694" s="12" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B694" s="11" t="s">
         <v>7</v>
@@ -16793,39 +16793,39 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695" s="12" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B695" s="11" t="s">
         <v>1319</v>
-      </c>
-      <c r="B695" s="11" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696" s="12" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B696" s="11" t="s">
         <v>1321</v>
-      </c>
-      <c r="B696" s="11" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B697" s="11" t="s">
         <v>1323</v>
-      </c>
-      <c r="B697" s="11" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698" s="12" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B698" s="11" t="s">
         <v>1325</v>
-      </c>
-      <c r="B698" s="11" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699" s="12" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B699" s="11" t="s">
         <v>7</v>
@@ -16833,42 +16833,42 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700" s="13" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B700" s="11" t="s">
         <v>1328</v>
-      </c>
-      <c r="B700" s="11" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701" s="12" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B701" s="11" t="s">
         <v>1330</v>
-      </c>
-      <c r="B701" s="11" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702" s="12" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B702" s="11" t="s">
         <v>1332</v>
-      </c>
-      <c r="B702" s="11" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703" s="12" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B703" s="11" t="s">
         <v>1334</v>
-      </c>
-      <c r="B703" s="11" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704" s="12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B704" s="11" t="s">
         <v>1336</v>
-      </c>
-      <c r="B704" s="11" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
@@ -16881,18 +16881,18 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706" s="13" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B706" s="11" t="s">
         <v>1338</v>
-      </c>
-      <c r="B706" s="11" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707" s="13" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B707" s="11" t="s">
         <v>1340</v>
-      </c>
-      <c r="B707" s="11" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.3">
@@ -16908,23 +16908,23 @@
         <v>423</v>
       </c>
       <c r="B709" s="11" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710" s="13" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B710" s="11" t="s">
         <v>1343</v>
-      </c>
-      <c r="B710" s="11" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A711" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B711" s="11" t="s">
         <v>1345</v>
-      </c>
-      <c r="B711" s="11" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
@@ -16945,7 +16945,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714" s="12" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B714" s="11" t="s">
         <v>7</v>
@@ -16956,15 +16956,15 @@
         <v>429</v>
       </c>
       <c r="B715" s="11" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716" s="12" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B716" s="11" t="s">
         <v>1349</v>
-      </c>
-      <c r="B716" s="11" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
@@ -16993,15 +16993,15 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720" s="12" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B720" s="11" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721" s="12" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B721" s="11" t="s">
         <v>7</v>
@@ -17009,87 +17009,87 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722" s="12" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B722" s="11" t="s">
         <v>1353</v>
-      </c>
-      <c r="B722" s="11" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723" s="12" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B723" s="11" t="s">
         <v>1355</v>
-      </c>
-      <c r="B723" s="11" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724" s="13" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B724" s="11" t="s">
         <v>1357</v>
-      </c>
-      <c r="B724" s="11" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725" s="12" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B725" s="11" t="s">
         <v>1359</v>
-      </c>
-      <c r="B725" s="11" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726" s="13" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B726" s="11" t="s">
         <v>1361</v>
-      </c>
-      <c r="B726" s="11" t="s">
-        <v>1362</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727" s="12" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B727" s="11" t="s">
         <v>1363</v>
-      </c>
-      <c r="B727" s="11" t="s">
-        <v>1364</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728" s="13" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B728" s="11" t="s">
         <v>1365</v>
-      </c>
-      <c r="B728" s="11" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729" s="13" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B729" s="11" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730" s="13" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B730" s="11" t="s">
         <v>1368</v>
-      </c>
-      <c r="B730" s="11" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731" s="13" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B731" s="11" t="s">
         <v>1370</v>
-      </c>
-      <c r="B731" s="11" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732" s="13" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B732" s="11" t="s">
         <v>24</v>
@@ -17097,23 +17097,23 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733" s="12" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B733" s="11" t="s">
         <v>1373</v>
-      </c>
-      <c r="B733" s="11" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734" s="13" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B734" s="11" t="s">
         <v>1375</v>
-      </c>
-      <c r="B734" s="11" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735" s="12" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B735" s="11" t="s">
         <v>7</v>
@@ -17129,15 +17129,15 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B737" s="11" t="s">
         <v>1378</v>
-      </c>
-      <c r="B737" s="11" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738" s="12" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B738" s="11" t="s">
         <v>316</v>
@@ -17161,23 +17161,23 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741" s="13" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B741" s="11" t="s">
         <v>1381</v>
-      </c>
-      <c r="B741" s="11" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742" s="12" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B742" s="11" t="s">
         <v>1383</v>
-      </c>
-      <c r="B742" s="11" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743" s="12" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B743" s="11" t="s">
         <v>454</v>
@@ -17185,10 +17185,10 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B744" s="11" t="s">
         <v>1386</v>
-      </c>
-      <c r="B744" s="11" t="s">
-        <v>1387</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.3">
@@ -17217,66 +17217,66 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748" s="13" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B748" s="11" t="s">
         <v>1388</v>
-      </c>
-      <c r="B748" s="11" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749" s="12" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B749" s="11" t="s">
         <v>1390</v>
-      </c>
-      <c r="B749" s="11" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A750" s="13" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B750" s="11" t="s">
         <v>1392</v>
-      </c>
-      <c r="B750" s="11" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A751" s="12" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B751" s="11" t="s">
         <v>1394</v>
-      </c>
-      <c r="B751" s="11" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752" s="13" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B752" s="11" t="s">
         <v>1396</v>
-      </c>
-      <c r="B752" s="11" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753" s="12" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B753" s="11" t="s">
         <v>1398</v>
-      </c>
-      <c r="B753" s="11" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B754" s="11" t="s">
         <v>1400</v>
-      </c>
-      <c r="B754" s="11" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755" s="12" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B755" s="11" t="s">
         <v>1402</v>
-      </c>
-      <c r="B755" s="11" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.3">
@@ -17321,34 +17321,34 @@
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761" s="13" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B761" s="11" t="s">
         <v>1404</v>
-      </c>
-      <c r="B761" s="11" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762" s="13" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B762" s="11" t="s">
         <v>1406</v>
-      </c>
-      <c r="B762" s="11" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763" s="13" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B763" s="11" t="s">
         <v>1408</v>
-      </c>
-      <c r="B763" s="11" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764" s="13" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B764" s="11" t="s">
         <v>1410</v>
-      </c>
-      <c r="B764" s="11" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.3">
@@ -17356,7 +17356,7 @@
         <v>502</v>
       </c>
       <c r="B765" s="11" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.3">
@@ -17417,26 +17417,26 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773" s="12" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B773" s="11" t="s">
         <v>1413</v>
-      </c>
-      <c r="B773" s="11" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774" s="13" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B774" s="11" t="s">
         <v>1415</v>
-      </c>
-      <c r="B774" s="11" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A775" s="12" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B775" s="11" t="s">
         <v>1417</v>
-      </c>
-      <c r="B775" s="11" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="776" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
@@ -17468,15 +17468,15 @@
         <v>475</v>
       </c>
       <c r="B779" s="11" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A780" s="13" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B780" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
@@ -17505,18 +17505,18 @@
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A784" s="12" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B784" s="11" t="s">
         <v>1421</v>
-      </c>
-      <c r="B784" s="11" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785" s="12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B785" s="11" t="s">
         <v>1423</v>
-      </c>
-      <c r="B785" s="11" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.3">
@@ -17529,66 +17529,66 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787" s="12" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B787" s="11" t="s">
         <v>1425</v>
-      </c>
-      <c r="B787" s="11" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788" s="12" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B788" s="11" t="s">
         <v>1427</v>
-      </c>
-      <c r="B788" s="11" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A789" s="12" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B789" s="11" t="s">
         <v>1429</v>
-      </c>
-      <c r="B789" s="11" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A790" s="12" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B790" s="11" t="s">
         <v>1431</v>
-      </c>
-      <c r="B790" s="11" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A791" s="12" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B791" s="11" t="s">
         <v>1433</v>
-      </c>
-      <c r="B791" s="11" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A792" s="12" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B792" s="11" t="s">
         <v>1435</v>
-      </c>
-      <c r="B792" s="11" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A793" s="12" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B793" s="11" t="s">
         <v>1437</v>
-      </c>
-      <c r="B793" s="11" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A794" s="12" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B794" s="11" t="s">
         <v>1439</v>
-      </c>
-      <c r="B794" s="11" t="s">
-        <v>1440</v>
       </c>
     </row>
   </sheetData>
@@ -17609,16 +17609,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="31" t="s">
         <v>1483</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="32"/>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
-        <v>1484</v>
-      </c>
-      <c r="B2" s="29"/>
+      <c r="A2" s="31" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
@@ -17629,39 +17629,39 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="26" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>1475</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>1479</v>
-      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="26" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>1476</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>1480</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="26" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>1477</v>
       </c>
-      <c r="B6" s="32" t="s">
-        <v>1481</v>
-      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="26" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>1478</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>1482</v>
-      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="30"/>
+      <c r="A8" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
